--- a/data/Verzasca/cost/cost_report.xlsx
+++ b/data/Verzasca/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>303.891449271367</v>
+        <v>248.1252537161147</v>
       </c>
       <c r="C2" t="n">
-        <v>24937.11379044956</v>
+        <v>25770.9200107598</v>
       </c>
       <c r="D2" t="n">
-        <v>-29499.08796192323</v>
+        <v>-30146.93917709118</v>
       </c>
       <c r="E2" t="n">
-        <v>5599.302672005976</v>
+        <v>3798.598103286315</v>
       </c>
       <c r="F2" t="n">
-        <v>38392.00205312658</v>
+        <v>37137.09828992975</v>
       </c>
       <c r="G2" t="n">
-        <v>39733.22200293026</v>
+        <v>36807.8024806008</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1166396458199221</v>
+        <v>2.593244944150952</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>309.3903953602425</v>
+        <v>245.8944208902199</v>
       </c>
       <c r="C3" t="n">
-        <v>14059.70304695432</v>
+        <v>25685.01810892107</v>
       </c>
       <c r="D3" t="n">
-        <v>1482.000833969492</v>
+        <v>-29294.40976155897</v>
       </c>
       <c r="E3" t="n">
-        <v>4287.971944809417</v>
+        <v>3884.929831052926</v>
       </c>
       <c r="F3" t="n">
-        <v>25144.98014843256</v>
+        <v>37759.37543390443</v>
       </c>
       <c r="G3" t="n">
-        <v>45284.04636952603</v>
+        <v>38280.80803320968</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.132934478091027</v>
+        <v>2.697023598256219</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>304.7627135170967</v>
+        <v>250.59564703507</v>
       </c>
       <c r="C4" t="n">
-        <v>23213.18936077429</v>
+        <v>13795.28501446516</v>
       </c>
       <c r="D4" t="n">
-        <v>-23646.185425213</v>
+        <v>3962.826095708961</v>
       </c>
       <c r="E4" t="n">
-        <v>4313.573538816596</v>
+        <v>2348.741120621757</v>
       </c>
       <c r="F4" t="n">
-        <v>36934.99771915567</v>
+        <v>22484.63213374342</v>
       </c>
       <c r="G4" t="n">
-        <v>41120.33790705064</v>
+        <v>42842.08001157437</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1207116213510243</v>
+        <v>3.018381970656358</v>
       </c>
     </row>
     <row r="5">
@@ -581,22 +581,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>309.8740218120283</v>
+        <v>252.2988603806543</v>
       </c>
       <c r="C5" t="n">
-        <v>14002.43244604002</v>
+        <v>13728.03086763431</v>
       </c>
       <c r="D5" t="n">
-        <v>2035.261939351194</v>
+        <v>4718.568635087694</v>
       </c>
       <c r="E5" t="n">
-        <v>4357.287737935563</v>
+        <v>2347.908430741636</v>
       </c>
       <c r="F5" t="n">
-        <v>25889.94989827556</v>
+        <v>23074.44464633739</v>
       </c>
       <c r="G5" t="n">
-        <v>46594.80604341437</v>
+        <v>44121.25144018169</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1367823045800567</v>
+        <v>3.108504298434186</v>
       </c>
     </row>
   </sheetData>
